--- a/public/staff_allocation_template.xlsx
+++ b/public/staff_allocation_template.xlsx
@@ -450,25 +450,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,62 +499,87 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-Jan</t>
+          <t>2026-August</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-Feb</t>
+          <t>2026-September</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-Mar</t>
+          <t>2026-October</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-Apr</t>
+          <t>2026-November</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-May</t>
+          <t>2026-December</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-Jun</t>
+          <t>2027-January</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2026-Jul</t>
+          <t>2027-February</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2026-Aug</t>
+          <t>2027-March</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
+          <t>2027-April</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>2026-Oct</t>
+          <t>2027-May</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>2026-Nov</t>
+          <t>2027-June</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>2026-Dec</t>
+          <t>2027-July</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2027-August</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2027-September</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2027-October</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2027-November</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2027-December</t>
         </is>
       </c>
     </row>
@@ -571,40 +601,55 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -625,40 +670,55 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -679,40 +739,55 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>100</v>
+        <v>15</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -733,40 +808,55 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -787,40 +877,400 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Samantha Reed</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Elena Rostova</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ADE</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Marcus Thorne</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>SRA</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -834,13 +1284,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -876,7 +1326,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-January</t>
+          <t>2026-August</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -896,12 +1346,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-March</t>
+          <t>2026-August</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-September</t>
+          <t>2026-October</t>
         </is>
       </c>
     </row>
@@ -916,12 +1366,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-June</t>
+          <t>2026-October</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-November</t>
+          <t>2027-March</t>
         </is>
       </c>
     </row>
@@ -936,12 +1386,92 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-January</t>
+          <t>2026-August</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-June</t>
+          <t>2026-November</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Quantum AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2027-January</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2027-June</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Shield Hardening</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2027-March</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2027-August</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Apex Mobile Suite</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2027-May</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2027-November</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Orion Data Pipeline</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2027-July</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2027-December</t>
         </is>
       </c>
     </row>
@@ -956,11 +1486,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1223,6 +1753,282 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Samantha Reed</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Quantum AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Elena Rostova</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Quantum AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Quantum AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Elena Rostova</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Shield Hardening</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Marcus Thorne</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Shield Hardening</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Shield Hardening</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Jordan Ellis</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Apex Mobile Suite</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Apex Mobile Suite</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Marcus Thorne</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Apex Mobile Suite</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Orion Data Pipeline</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Samantha Reed</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Orion Data Pipeline</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Taylor Chen</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Orion Data Pipeline</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/staff_allocation_template.xlsx
+++ b/public/staff_allocation_template.xlsx
@@ -601,13 +601,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>50</v>
@@ -628,25 +628,25 @@
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U2" s="4" t="n">
         <v>0</v>
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>25</v>
@@ -685,13 +685,13 @@
         <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>0</v>
@@ -739,28 +739,28 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -772,22 +772,22 @@
         <v>0</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -808,19 +808,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>50</v>
@@ -973,28 +973,28 @@
         <v>50</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
@@ -1030,40 +1030,40 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -1099,22 +1099,22 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>50</v>
@@ -1174,31 +1174,31 @@
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1243,34 +1243,34 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1486,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1594,11 +1594,11 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Taylor Chen</t>
+          <t>Jordan Ellis</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -1617,11 +1617,11 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Jordan Ellis</t>
+          <t>Taylor Chen</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -1640,19 +1640,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Riley Harper</t>
+          <t>Alex Mercer</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Helios Analytics Platform</t>
+          <t>Vanguard Cloud Portal</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1663,19 +1663,19 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Taylor Chen</t>
+          <t>Riley Harper</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Helios Analytics Platform</t>
+          <t>Vanguard Cloud Portal</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1686,11 +1686,11 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Morgan Vance</t>
+          <t>Riley Harper</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1703,63 +1703,63 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>PL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Alex Mercer</t>
+          <t>Taylor Chen</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Cloud Portal</t>
+          <t>Helios Analytics Platform</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Riley Harper</t>
+          <t>Samantha Reed</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Vanguard Cloud Portal</t>
+          <t>Quantum AI Infrastructure</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>PL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Samantha Reed</t>
+          <t>Elena Rostova</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Elena Rostova</t>
+          <t>David Kim</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1795,40 +1795,40 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>David Kim</t>
+          <t>Elena Rostova</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Quantum AI Infrastructure</t>
+          <t>Cyber Shield Hardening</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>PL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Elena Rostova</t>
+          <t>Marcus Thorne</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1841,71 +1841,71 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Marcus Thorne</t>
+          <t>Samantha Reed</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Cyber Shield Hardening</t>
+          <t>Apex Mobile Suite</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>PL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Marcus Thorne</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Cyber Shield Hardening</t>
+          <t>Apex Mobile Suite</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>PL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Jordan Ellis</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Apex Mobile Suite</t>
+          <t>Orion Data Pipeline</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1924,108 +1924,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Apex Mobile Suite</t>
+          <t>Orion Data Pipeline</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Marcus Thorne</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Apex Mobile Suite</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Priya Patel</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Orion Data Pipeline</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Samantha Reed</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Orion Data Pipeline</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Taylor Chen</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Orion Data Pipeline</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
         </is>
       </c>
     </row>

--- a/public/staff_allocation_template.xlsx
+++ b/public/staff_allocation_template.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Staff" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Projects" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Assignments" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Roles" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1940,4 +1941,82 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Role Code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Role Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Project Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Member</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Assisting</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DOR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Director of Research</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/staff_allocation_template.xlsx
+++ b/public/staff_allocation_template.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Staff" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Projects" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Assignments" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Roles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Designations" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1949,68 +1949,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Role Code</t>
+          <t>Designation Code</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Role Name</t>
+          <t>Designation Name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Project Lead</t>
+          <t>Research Associate</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SRA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Member</t>
+          <t>Senior Research Associate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>DOR</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Assisting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>DOR</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Director of Research</t>
         </is>
